--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
@@ -562,16 +562,19 @@
         <v>25</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +588,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>8.6</v>
@@ -685,7 +691,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
@@ -656,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
@@ -665,7 +665,7 @@
         <v>88</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20231.xlsx
@@ -665,7 +665,7 @@
         <v>88</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
